--- a/solucoes/benchmarks.xlsx
+++ b/solucoes/benchmarks.xlsx
@@ -349,7 +349,7 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Y8"/>
+  <dimension ref="A1:Z12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="18.00390625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -375,110 +375,115 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>element</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>dt</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>reynolds</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>iterations</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>npoints</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>ne</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>device</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>tempo_total_s</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>tempo_assembly_s</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>tempo_medio_por_iter_s</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>bicg_iters_media</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>bicg_iters_max</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>bicg_residual_media</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>bicg_residual_max</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>passos_nao_convergidos</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>vel_l2_media</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>vel_l2_max</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>vel_linf_max</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>divergencia_l2_media</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>divergencia_l2_max</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pressao_min</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pressao_max</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pressao_media</t>
         </is>
@@ -500,72 +505,72 @@
           <t>explicit</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>0.001</v>
       </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
       <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
         <v>1000</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>2785</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>5376</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>cuda</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>48.877</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>0.899</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>0.04798</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>69.22</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>812</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>4.215317621768152e-08</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>3.23688959567081e-05</v>
       </c>
-      <c r="Q2" t="n">
-        <v>1</v>
-      </c>
       <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="n">
         <v>1.039509378147781</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>1.04030074733469</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>1.453958156096538</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>1.120349890657455e-06</v>
       </c>
-      <c r="V2" t="n">
+      <c r="W2" t="n">
         <v>7.214415151496963e-06</v>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>0</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Y2" t="n">
         <v>89.90965345641072</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12.0704947104741</v>
       </c>
     </row>
@@ -585,72 +590,72 @@
           <t>explicit</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>0.001</v>
       </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
       <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
         <v>1000</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>2785</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>5376</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>cuda</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>47.83</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>0.962</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>0.04687</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>70.63</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>800</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>9.61675967205934e-09</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>9.994718745111667e-09</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>0</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>1.039511131776279</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>1.040302560702422</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>1.453985464000669</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>1.120271924695479e-06</v>
       </c>
-      <c r="V3" t="n">
+      <c r="W3" t="n">
         <v>7.214415151496963e-06</v>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>0</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Y3" t="n">
         <v>89.90807160795119</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12.0692699991507</v>
       </c>
     </row>
@@ -670,72 +675,72 @@
           <t>semi_lagrangian</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>0.001</v>
       </c>
-      <c r="E4" t="n">
-        <v>1</v>
-      </c>
       <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
         <v>1000</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>2785</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>5376</v>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>cuda</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>38.664</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>0.9340000000000001</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>0.03773</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>70.38</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>831</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>9.766923238486063e-09</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>9.997798030148422e-09</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>0</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>1.039477118287105</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>1.040267269285854</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>1.453849048051091</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>1.123509111659083e-06</v>
       </c>
-      <c r="V4" t="n">
+      <c r="W4" t="n">
         <v>7.214415145463838e-06</v>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>0</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Y4" t="n">
         <v>90.06113859597539</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12.08471465876959</v>
       </c>
     </row>
@@ -755,72 +760,72 @@
           <t>explicit</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>0.01</v>
       </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
       <c r="F5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" t="n">
         <v>1000</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>4497</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>8704</v>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>cuda</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>78.875</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>0.883</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>0.07799</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>95.34999999999999</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>1728</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>9.483307294568742e-09</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>7.782406738668755e-08</v>
       </c>
-      <c r="Q5" t="n">
-        <v>1</v>
-      </c>
       <c r="R5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S5" t="n">
         <v>0.6146985972660964</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>0.6148769871197257</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>1.398296977523984</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>7.533923959532594e-07</v>
       </c>
-      <c r="V5" t="n">
+      <c r="W5" t="n">
         <v>3.705599267467093e-06</v>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>-2.604872371500922</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Y5" t="n">
         <v>57.03158497092567</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>5.977230778103425</v>
       </c>
     </row>
@@ -840,72 +845,72 @@
           <t>semi_lagrangian</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>0.01</v>
       </c>
-      <c r="E6" t="n">
-        <v>1</v>
-      </c>
       <c r="F6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" t="n">
         <v>1000</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>4497</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>8704</v>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>cuda</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>49.895</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>0.931</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>0.04896</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>94.19</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>1884</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>9.364957723551908e-09</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>9.995339412144749e-09</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>0</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>0.6146621493851491</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>0.6148401635731089</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>1.397694512722004</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>7.552855668813309e-07</v>
       </c>
-      <c r="V6" t="n">
+      <c r="W6" t="n">
         <v>3.705599359542572e-06</v>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>-2.634100812132654</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Y6" t="n">
         <v>57.26405483042234</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>5.990895745727521</v>
       </c>
     </row>
@@ -925,72 +930,72 @@
           <t>explicit</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>0.01</v>
       </c>
-      <c r="E7" t="n">
-        <v>1</v>
-      </c>
       <c r="F7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" t="n">
         <v>1000</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>8321</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>16384</v>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>cuda</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>136.483</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>4.587</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>0.1319</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>49.43</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>2000</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>6.567866003586633e-06</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>0.005917582426095339</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>17</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>0.2615124286321051</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>0.2616749101577919</v>
       </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
       <c r="U7" t="n">
+        <v>1</v>
+      </c>
+      <c r="V7" t="n">
         <v>2.428001339631544e-09</v>
       </c>
-      <c r="V7" t="n">
+      <c r="W7" t="n">
         <v>2.378252693829666e-06</v>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>-163.0604278627739</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Y7" t="n">
         <v>163.0887978253157</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>-0.3520540115310006</v>
       </c>
     </row>
@@ -1010,73 +1015,433 @@
           <t>semi_lagrangian</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>0.01</v>
       </c>
-      <c r="E8" t="n">
-        <v>1</v>
-      </c>
       <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="n">
         <v>1000</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>8321</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>16384</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>cuda</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>33.632</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>1.052</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>0.03258</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>48.98</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>2000</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>5.808223674485787e-06</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>0.00433895624745374</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>17</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>0.2615004403370756</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>0.2616615660296004</v>
       </c>
-      <c r="T8" t="n">
-        <v>1</v>
-      </c>
       <c r="U8" t="n">
+        <v>1</v>
+      </c>
+      <c r="V8" t="n">
         <v>1.906247316280675e-09</v>
       </c>
-      <c r="V8" t="n">
+      <c r="W8" t="n">
         <v>1.654198689672881e-06</v>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>-163.1154479040269</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Y8" t="n">
         <v>163.1225856457656</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>-0.3523167436195234</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-14T21:00:04</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>meshes/degrau.msh</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>explicit</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>mini</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H9" t="n">
+        <v>4497</v>
+      </c>
+      <c r="I9" t="n">
+        <v>8704</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>cuda</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>76.84</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.888</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.07595</v>
+      </c>
+      <c r="N9" t="n">
+        <v>95.34999999999999</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1728</v>
+      </c>
+      <c r="P9" t="n">
+        <v>9.483307294568742e-09</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>7.782406738668755e-08</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.6146985972660964</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.6148769871197257</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.398296977523984</v>
+      </c>
+      <c r="V9" t="n">
+        <v>7.533923959532594e-07</v>
+      </c>
+      <c r="W9" t="n">
+        <v>3.705599267467093e-06</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-2.604872371500922</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>57.03158497092567</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>5.977230778103425</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-14T21:01:58</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>meshes/degrau.msh</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>explicit</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>tri6</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4497</v>
+      </c>
+      <c r="I10" t="n">
+        <v>8704</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>cuda</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>111.905</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.919</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.11099</v>
+      </c>
+      <c r="N10" t="n">
+        <v>113.38</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2000</v>
+      </c>
+      <c r="P10" t="n">
+        <v>9.729492680849292e-09</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.397269328001335e-08</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.6407328407656742</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.6409214968292722</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.456445355701974</v>
+      </c>
+      <c r="V10" t="n">
+        <v>4.999704935267258e-10</v>
+      </c>
+      <c r="W10" t="n">
+        <v>4.788437298733987e-08</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-99.7733691849418</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.040815509469854</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>-6.259566758620216</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-16T16:30:34</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>meshes/degrau.msh</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>explicit</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>mini</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4497</v>
+      </c>
+      <c r="I11" t="n">
+        <v>8704</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>cuda</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>83.498</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.917</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.08258</v>
+      </c>
+      <c r="N11" t="n">
+        <v>95.34999999999999</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1728</v>
+      </c>
+      <c r="P11" t="n">
+        <v>9.483307294568742e-09</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>7.782406738668755e-08</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.6146985972660964</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.6148769871197257</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.398296977523984</v>
+      </c>
+      <c r="V11" t="n">
+        <v>7.533923959532594e-07</v>
+      </c>
+      <c r="W11" t="n">
+        <v>3.705599267467093e-06</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-2.604872371500922</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>57.03158497092567</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>5.977230778103425</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-16T16:33:19</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>meshes/degrau.msh</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>explicit</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>tri6</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H12" t="n">
+        <v>4497</v>
+      </c>
+      <c r="I12" t="n">
+        <v>8704</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>cuda</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>143.581</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.914</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.14267</v>
+      </c>
+      <c r="N12" t="n">
+        <v>108.78</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.769001044260097e-06</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.001735817712656526</v>
+      </c>
+      <c r="R12" t="n">
+        <v>5</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.6407336020775738</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0.6409214920611498</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.456444420361531</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.280240130201723e-09</v>
+      </c>
+      <c r="W12" t="n">
+        <v>6.715700782185119e-07</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-2.040817099850358</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>99.77336789580126</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>6.259565760124965</v>
       </c>
     </row>
   </sheetData>

--- a/solucoes/benchmarks.xlsx
+++ b/solucoes/benchmarks.xlsx
@@ -349,7 +349,7 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Z12"/>
+  <dimension ref="A1:AA20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="18.00390625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -375,115 +375,120 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>sl_boundary</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>element</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>dt</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>reynolds</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>iterations</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>npoints</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ne</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>device</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>tempo_total_s</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>tempo_assembly_s</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>tempo_medio_por_iter_s</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>bicg_iters_media</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>bicg_iters_max</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>bicg_residual_media</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>bicg_residual_max</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>passos_nao_convergidos</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>vel_l2_media</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>vel_l2_max</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>vel_linf_max</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>divergencia_l2_media</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>divergencia_l2_max</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pressao_min</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pressao_max</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pressao_media</t>
         </is>
@@ -505,72 +510,72 @@
           <t>explicit</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>0.001</v>
       </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
       <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
         <v>1000</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>2785</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>5376</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>cuda</t>
         </is>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>48.877</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>0.899</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>0.04798</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>69.22</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>812</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>4.215317621768152e-08</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>3.23688959567081e-05</v>
       </c>
-      <c r="R2" t="n">
-        <v>1</v>
-      </c>
       <c r="S2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
         <v>1.039509378147781</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>1.04030074733469</v>
       </c>
-      <c r="U2" t="n">
+      <c r="V2" t="n">
         <v>1.453958156096538</v>
       </c>
-      <c r="V2" t="n">
+      <c r="W2" t="n">
         <v>1.120349890657455e-06</v>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>7.214415151496963e-06</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Y2" t="n">
         <v>0</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>89.90965345641072</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AA2" t="n">
         <v>12.0704947104741</v>
       </c>
     </row>
@@ -590,72 +595,72 @@
           <t>explicit</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>0.001</v>
       </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
       <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
         <v>1000</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>2785</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>5376</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>cuda</t>
         </is>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>47.83</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>0.962</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>0.04687</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>70.63</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>800</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>9.61675967205934e-09</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>9.994718745111667e-09</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>0</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>1.039511131776279</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>1.040302560702422</v>
       </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
         <v>1.453985464000669</v>
       </c>
-      <c r="V3" t="n">
+      <c r="W3" t="n">
         <v>1.120271924695479e-06</v>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>7.214415151496963e-06</v>
       </c>
-      <c r="X3" t="n">
+      <c r="Y3" t="n">
         <v>0</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>89.90807160795119</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AA3" t="n">
         <v>12.0692699991507</v>
       </c>
     </row>
@@ -675,72 +680,72 @@
           <t>semi_lagrangian</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>0.001</v>
       </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
       <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
         <v>1000</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>2785</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>5376</v>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>cuda</t>
         </is>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>38.664</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>0.9340000000000001</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>0.03773</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>70.38</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>831</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>9.766923238486063e-09</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>9.997798030148422e-09</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>0</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>1.039477118287105</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>1.040267269285854</v>
       </c>
-      <c r="U4" t="n">
+      <c r="V4" t="n">
         <v>1.453849048051091</v>
       </c>
-      <c r="V4" t="n">
+      <c r="W4" t="n">
         <v>1.123509111659083e-06</v>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>7.214415145463838e-06</v>
       </c>
-      <c r="X4" t="n">
+      <c r="Y4" t="n">
         <v>0</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>90.06113859597539</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AA4" t="n">
         <v>12.08471465876959</v>
       </c>
     </row>
@@ -760,72 +765,72 @@
           <t>explicit</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>0.01</v>
       </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
       <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
         <v>1000</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>4497</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>8704</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>cuda</t>
         </is>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>78.875</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>0.883</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>0.07799</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>95.34999999999999</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>1728</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>9.483307294568742e-09</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>7.782406738668755e-08</v>
       </c>
-      <c r="R5" t="n">
-        <v>1</v>
-      </c>
       <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
         <v>0.6146985972660964</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>0.6148769871197257</v>
       </c>
-      <c r="U5" t="n">
+      <c r="V5" t="n">
         <v>1.398296977523984</v>
       </c>
-      <c r="V5" t="n">
+      <c r="W5" t="n">
         <v>7.533923959532594e-07</v>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>3.705599267467093e-06</v>
       </c>
-      <c r="X5" t="n">
+      <c r="Y5" t="n">
         <v>-2.604872371500922</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>57.03158497092567</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AA5" t="n">
         <v>5.977230778103425</v>
       </c>
     </row>
@@ -845,72 +850,72 @@
           <t>semi_lagrangian</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>0.01</v>
       </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
       <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
         <v>1000</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>4497</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>8704</v>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>cuda</t>
         </is>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>49.895</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>0.931</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>0.04896</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>94.19</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>1884</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>9.364957723551908e-09</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>9.995339412144749e-09</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>0</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>0.6146621493851491</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>0.6148401635731089</v>
       </c>
-      <c r="U6" t="n">
+      <c r="V6" t="n">
         <v>1.397694512722004</v>
       </c>
-      <c r="V6" t="n">
+      <c r="W6" t="n">
         <v>7.552855668813309e-07</v>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>3.705599359542572e-06</v>
       </c>
-      <c r="X6" t="n">
+      <c r="Y6" t="n">
         <v>-2.634100812132654</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>57.26405483042234</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AA6" t="n">
         <v>5.990895745727521</v>
       </c>
     </row>
@@ -930,72 +935,72 @@
           <t>explicit</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>0.01</v>
       </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
       <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
         <v>1000</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>8321</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>16384</v>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>cuda</t>
         </is>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>136.483</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>4.587</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>0.1319</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>49.43</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>2000</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>6.567866003586633e-06</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>0.005917582426095339</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>17</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>0.2615124286321051</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>0.2616749101577919</v>
       </c>
-      <c r="U7" t="n">
-        <v>1</v>
-      </c>
       <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="n">
         <v>2.428001339631544e-09</v>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>2.378252693829666e-06</v>
       </c>
-      <c r="X7" t="n">
+      <c r="Y7" t="n">
         <v>-163.0604278627739</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>163.0887978253157</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AA7" t="n">
         <v>-0.3520540115310006</v>
       </c>
     </row>
@@ -1015,72 +1020,72 @@
           <t>semi_lagrangian</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>0.01</v>
       </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
       <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
         <v>1000</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>8321</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>16384</v>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>cuda</t>
         </is>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>33.632</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>1.052</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>0.03258</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>48.98</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>2000</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>5.808223674485787e-06</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>0.00433895624745374</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>17</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>0.2615004403370756</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>0.2616615660296004</v>
       </c>
-      <c r="U8" t="n">
-        <v>1</v>
-      </c>
       <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
         <v>1.906247316280675e-09</v>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>1.654198689672881e-06</v>
       </c>
-      <c r="X8" t="n">
+      <c r="Y8" t="n">
         <v>-163.1154479040269</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>163.1225856457656</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AA8" t="n">
         <v>-0.3523167436195234</v>
       </c>
     </row>
@@ -1100,77 +1105,77 @@
           <t>explicit</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>mini</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>0.01</v>
       </c>
-      <c r="F9" t="n">
-        <v>1</v>
-      </c>
       <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
         <v>1000</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>4497</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>8704</v>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>cuda</t>
         </is>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>76.84</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>0.888</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>0.07595</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>95.34999999999999</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>1728</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>9.483307294568742e-09</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>7.782406738668755e-08</v>
       </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
       <c r="S9" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
         <v>0.6146985972660964</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>0.6148769871197257</v>
       </c>
-      <c r="U9" t="n">
+      <c r="V9" t="n">
         <v>1.398296977523984</v>
       </c>
-      <c r="V9" t="n">
+      <c r="W9" t="n">
         <v>7.533923959532594e-07</v>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>3.705599267467093e-06</v>
       </c>
-      <c r="X9" t="n">
+      <c r="Y9" t="n">
         <v>-2.604872371500922</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>57.03158497092567</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AA9" t="n">
         <v>5.977230778103425</v>
       </c>
     </row>
@@ -1190,77 +1195,77 @@
           <t>explicit</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>tri6</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>0.01</v>
       </c>
-      <c r="F10" t="n">
-        <v>1</v>
-      </c>
       <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
         <v>1000</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>4497</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>8704</v>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>cuda</t>
         </is>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>111.905</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>0.919</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>0.11099</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>113.38</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>2000</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>9.729492680849292e-09</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>1.397269328001335e-08</v>
       </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
       <c r="S10" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
         <v>0.6407328407656742</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>0.6409214968292722</v>
       </c>
-      <c r="U10" t="n">
+      <c r="V10" t="n">
         <v>1.456445355701974</v>
       </c>
-      <c r="V10" t="n">
+      <c r="W10" t="n">
         <v>4.999704935267258e-10</v>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>4.788437298733987e-08</v>
       </c>
-      <c r="X10" t="n">
+      <c r="Y10" t="n">
         <v>-99.7733691849418</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>2.040815509469854</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AA10" t="n">
         <v>-6.259566758620216</v>
       </c>
     </row>
@@ -1280,77 +1285,77 @@
           <t>explicit</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>mini</t>
         </is>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>0.01</v>
       </c>
-      <c r="F11" t="n">
-        <v>1</v>
-      </c>
       <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
         <v>1000</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>4497</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>8704</v>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>cuda</t>
         </is>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>83.498</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>0.917</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>0.08258</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>95.34999999999999</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>1728</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>9.483307294568742e-09</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>7.782406738668755e-08</v>
       </c>
-      <c r="R11" t="n">
-        <v>1</v>
-      </c>
       <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
         <v>0.6146985972660964</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>0.6148769871197257</v>
       </c>
-      <c r="U11" t="n">
+      <c r="V11" t="n">
         <v>1.398296977523984</v>
       </c>
-      <c r="V11" t="n">
+      <c r="W11" t="n">
         <v>7.533923959532594e-07</v>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>3.705599267467093e-06</v>
       </c>
-      <c r="X11" t="n">
+      <c r="Y11" t="n">
         <v>-2.604872371500922</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>57.03158497092567</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AA11" t="n">
         <v>5.977230778103425</v>
       </c>
     </row>
@@ -1370,78 +1375,838 @@
           <t>explicit</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>tri6</t>
         </is>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>0.01</v>
       </c>
-      <c r="F12" t="n">
-        <v>1</v>
-      </c>
       <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
         <v>1000</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>4497</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>8704</v>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>cuda</t>
         </is>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>143.581</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>0.914</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>0.14267</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>108.78</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>2000</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>1.769001044260097e-06</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>0.001735817712656526</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>5</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>0.6407336020775738</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>0.6409214920611498</v>
       </c>
-      <c r="U12" t="n">
+      <c r="V12" t="n">
         <v>1.456444420361531</v>
       </c>
-      <c r="V12" t="n">
+      <c r="W12" t="n">
         <v>1.280240130201723e-09</v>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>6.715700782185119e-07</v>
       </c>
-      <c r="X12" t="n">
+      <c r="Y12" t="n">
         <v>-2.040817099850358</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>99.77336789580126</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AA12" t="n">
         <v>6.259565760124965</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-16T17:11:01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>meshes/degrau.msh</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>semi_lagrangian</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>dirichlet</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>mini</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4497</v>
+      </c>
+      <c r="J13" t="n">
+        <v>8704</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>cuda</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>50.015</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.0491</v>
+      </c>
+      <c r="O13" t="n">
+        <v>94.19</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1884</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>9.364957723551908e-09</v>
+      </c>
+      <c r="R13" t="n">
+        <v>9.995339412144749e-09</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0.6146621493851491</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.6148401635731089</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.397694512722004</v>
+      </c>
+      <c r="W13" t="n">
+        <v>7.552855668813309e-07</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3.705599359542572e-06</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>-2.634100812132654</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>57.26405483042234</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>5.990895745727521</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-16T17:11:54</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>meshes/degrau.msh</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>semi_lagrangian</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>intercept</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>mini</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I14" t="n">
+        <v>4497</v>
+      </c>
+      <c r="J14" t="n">
+        <v>8704</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>cuda</t>
+        </is>
+      </c>
+      <c r="L14" t="n">
+        <v>50.564</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.918</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.04965</v>
+      </c>
+      <c r="O14" t="n">
+        <v>94.19</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1884</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>9.364957723551908e-09</v>
+      </c>
+      <c r="R14" t="n">
+        <v>9.995339412144749e-09</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0.6146621493851491</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.6148401635731089</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.397694512722004</v>
+      </c>
+      <c r="W14" t="n">
+        <v>7.552855668813309e-07</v>
+      </c>
+      <c r="X14" t="n">
+        <v>3.705599359542572e-06</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>-2.634100812132654</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>57.26405483042234</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>5.990895745727521</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-16T17:15:06</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>meshes/degrau.msh</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>semi_lagrangian</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>dirichlet</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>mini</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>100</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4497</v>
+      </c>
+      <c r="J15" t="n">
+        <v>8704</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>cuda</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>14.559</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.13649</v>
+      </c>
+      <c r="O15" t="n">
+        <v>258.05</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2000</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.459350060528139e-06</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.0002071776133085939</v>
+      </c>
+      <c r="S15" t="n">
+        <v>7</v>
+      </c>
+      <c r="T15" t="n">
+        <v>0.6146438906272188</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.6148445863174624</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.39750109127615</v>
+      </c>
+      <c r="W15" t="n">
+        <v>7.540616543498233e-07</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.270006265697892e-06</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>-2.714167577826022</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>57.18473756356989</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>5.984136830788484</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-16T17:15:22</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>meshes/degrau.msh</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>semi_lagrangian</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>intercept</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>mini</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>100</v>
+      </c>
+      <c r="I16" t="n">
+        <v>4497</v>
+      </c>
+      <c r="J16" t="n">
+        <v>8704</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>cuda</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>14.266</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.904</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.13362</v>
+      </c>
+      <c r="O16" t="n">
+        <v>253.34</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2000</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.712110669591582e-06</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.0001334787618014219</v>
+      </c>
+      <c r="S16" t="n">
+        <v>7</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.6146243642602109</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.6148246621165131</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.397419307799288</v>
+      </c>
+      <c r="W16" t="n">
+        <v>7.540118773328026e-07</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.270006265697892e-06</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>-2.714152490092553</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>57.28072892821958</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>5.985080637758643</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-16T17:38:52</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>meshes/degrau.msh</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>semi_lagrangian</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>intercept</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>mini</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>20</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4497</v>
+      </c>
+      <c r="J17" t="n">
+        <v>8704</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>cuda</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>18.382</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1.957</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.82126</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1688.2</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2000</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.479874692295614e-08</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.225067130380513e-07</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.6064971992631448</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.6143835829200134</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.398262540501071</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.241347311098037e-06</v>
+      </c>
+      <c r="X17" t="n">
+        <v>4.752847116415959e-06</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>-1.621306548257845</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>61.3035338236619</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>6.076737548028509</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-16T17:39:21</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>meshes/degrau.msh</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>semi_lagrangian</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>intercept</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>mini</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>20</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4497</v>
+      </c>
+      <c r="J18" t="n">
+        <v>8704</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>cuda</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>15.02</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2.014</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.65028</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1361.85</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1884</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>8.98761850764543e-09</v>
+      </c>
+      <c r="R18" t="n">
+        <v>9.988942916466912e-09</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.606134055596247</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.6140432094621265</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.397694512722004</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.145105468806884e-06</v>
+      </c>
+      <c r="X18" t="n">
+        <v>3.705599359542572e-06</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>-2.53014377829447</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>57.39646416922103</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>6.066931267082078</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-16T17:51:42</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>meshes/degrau.msh</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>semi_lagrangian</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>intercept</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>mini</t>
+        </is>
+      </c>
+      <c r="F19" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>40</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4497</v>
+      </c>
+      <c r="J19" t="n">
+        <v>8704</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>cuda</t>
+        </is>
+      </c>
+      <c r="L19" t="n">
+        <v>34.41</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.984</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.81066</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1738.15</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2000</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1.25160213084795e-08</v>
+      </c>
+      <c r="R19" t="n">
+        <v>5.478332438025377e-08</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.6105343062093435</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.6151839063541764</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.399747335011143</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.003865971071817e-06</v>
+      </c>
+      <c r="X19" t="n">
+        <v>4.752846739697811e-06</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>-1.747773575566981</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>61.26329776161139</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>6.012170301938741</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-16T17:53:33</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>meshes/degrau.msh</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>semi_lagrangian</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>intercept</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>mini</t>
+        </is>
+      </c>
+      <c r="F20" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>20</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4497</v>
+      </c>
+      <c r="J20" t="n">
+        <v>8704</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>cuda</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>14.533</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.964</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.62846</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1361.85</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1884</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>8.98761850764543e-09</v>
+      </c>
+      <c r="R20" t="n">
+        <v>9.988942916466912e-09</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.606134055596247</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.6140432094621265</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.397694512722004</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.145105468806884e-06</v>
+      </c>
+      <c r="X20" t="n">
+        <v>3.705599359542572e-06</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>-2.53014377829447</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>57.39646416922103</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>6.066931267082078</v>
       </c>
     </row>
   </sheetData>

--- a/solucoes/benchmarks.xlsx
+++ b/solucoes/benchmarks.xlsx
@@ -349,7 +349,7 @@
     <outlinePr applyStyles="0" summaryBelow="1" summaryRight="1" showOutlineSymbols="1"/>
     <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:AA20"/>
+  <dimension ref="A1:AA23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="18.00390625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -2209,6 +2209,291 @@
         <v>6.066931267082078</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-16T21:34:23</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>meshes/poiseuille.msh</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>semi_lagrangian</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>intercept</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>mini</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2785</v>
+      </c>
+      <c r="J21" t="n">
+        <v>5376</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>cuda</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>38.48</v>
+      </c>
+      <c r="M21" t="n">
+        <v>2.004</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.03648</v>
+      </c>
+      <c r="O21" t="n">
+        <v>70.59999999999999</v>
+      </c>
+      <c r="P21" t="n">
+        <v>817</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>1.096164163114042e-08</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.26519273662047e-06</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.014312173002553</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.015097340570476</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.086090425456429e-06</v>
+      </c>
+      <c r="X21" t="n">
+        <v>6.973924092259127e-06</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>23.28471639213366</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>11.13658742875826</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-16T21:40:53</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>meshes/poiseuille.msh</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>semi_lagrangian</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>intercept</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>mini</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2785</v>
+      </c>
+      <c r="J22" t="n">
+        <v>5376</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>cuda</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>38.824</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1.988</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.03684</v>
+      </c>
+      <c r="O22" t="n">
+        <v>70.45</v>
+      </c>
+      <c r="P22" t="n">
+        <v>822</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>9.04916365425379e-09</v>
+      </c>
+      <c r="R22" t="n">
+        <v>9.995951224299408e-09</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.07862146407123</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.079454739135939</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.158598878063063e-06</v>
+      </c>
+      <c r="X22" t="n">
+        <v>7.43985636160254e-06</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>23.95445549632578</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>11.98663452667206</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-16T21:47:09</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>meshes/poiseuille.msh</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>semi_lagrangian</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>intercept</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>mini</t>
+        </is>
+      </c>
+      <c r="F23" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2785</v>
+      </c>
+      <c r="J23" t="n">
+        <v>5376</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>cuda</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>374.177</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2.006</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.37217</v>
+      </c>
+      <c r="O23" t="n">
+        <v>717.53</v>
+      </c>
+      <c r="P23" t="n">
+        <v>928</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>8.866194877452315e-09</v>
+      </c>
+      <c r="R23" t="n">
+        <v>9.999740402133139e-09</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.078738408295607</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.079610753318657</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.193589975856533e-06</v>
+      </c>
+      <c r="X23" t="n">
+        <v>6.560389253812059e-06</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>24.13350125457942</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>12.01016718663609</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
